--- a/Project 1 Data Quality Assessment/D4 Parallel-redundancy Temporal Consistency/outputs/figure_source_data/FigD4_2_pair_mechanism_profile_source_data.xlsx
+++ b/Project 1 Data Quality Assessment/D4 Parallel-redundancy Temporal Consistency/outputs/figure_source_data/FigD4_2_pair_mechanism_profile_source_data.xlsx
@@ -482,16 +482,16 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>3.818166776968895</v>
+        <v>4.094242575078812</v>
       </c>
       <c r="E2" t="n">
         <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G2" t="n">
-        <v>6044</v>
+        <v>6027</v>
       </c>
     </row>
     <row r="3">
@@ -509,7 +509,7 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>4.068001323626738</v>
+        <v>4.097892815662851</v>
       </c>
       <c r="E3" t="n">
         <v>4</v>
@@ -518,7 +518,7 @@
         <v>5</v>
       </c>
       <c r="G3" t="n">
-        <v>6044</v>
+        <v>6027</v>
       </c>
     </row>
     <row r="4">
@@ -533,10 +533,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>4.120946393117141</v>
+        <v>4.140700182512029</v>
       </c>
       <c r="E4" t="n">
         <v>4</v>
@@ -545,7 +545,7 @@
         <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>6044</v>
+        <v>6027</v>
       </c>
     </row>
     <row r="5">
@@ -563,7 +563,7 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>2.78590337524818</v>
+        <v>2.787290525966484</v>
       </c>
       <c r="E5" t="n">
         <v>2</v>
@@ -572,7 +572,7 @@
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>6044</v>
+        <v>6027</v>
       </c>
     </row>
     <row r="6">
@@ -590,16 +590,16 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>4.221009098428453</v>
+        <v>4.405176704828273</v>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F6" t="n">
         <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>6045</v>
+        <v>6027</v>
       </c>
     </row>
     <row r="7">
@@ -617,16 +617,16 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>4.054755996691481</v>
+        <v>4.086112493777999</v>
       </c>
       <c r="E7" t="n">
         <v>4</v>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G7" t="n">
-        <v>6045</v>
+        <v>6027</v>
       </c>
     </row>
     <row r="8">
@@ -644,7 +644,7 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>3.954011579818031</v>
+        <v>4.003816160610586</v>
       </c>
       <c r="E8" t="n">
         <v>4</v>
@@ -653,7 +653,7 @@
         <v>4</v>
       </c>
       <c r="G8" t="n">
-        <v>6045</v>
+        <v>6027</v>
       </c>
     </row>
     <row r="9">
@@ -671,7 +671,7 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>2.627295285359801</v>
+        <v>2.640451302472208</v>
       </c>
       <c r="E9" t="n">
         <v>2</v>
@@ -680,7 +680,7 @@
         <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>6045</v>
+        <v>6027</v>
       </c>
     </row>
     <row r="10">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>4.003639371381307</v>
+        <v>4.264476522316244</v>
       </c>
       <c r="E10" t="n">
         <v>4</v>
@@ -707,7 +707,7 @@
         <v>5</v>
       </c>
       <c r="G10" t="n">
-        <v>6045</v>
+        <v>6027</v>
       </c>
     </row>
     <row r="11">
@@ -725,7 +725,7 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>3.858726220016543</v>
+        <v>3.915380786460926</v>
       </c>
       <c r="E11" t="n">
         <v>4</v>
@@ -734,7 +734,7 @@
         <v>4</v>
       </c>
       <c r="G11" t="n">
-        <v>6045</v>
+        <v>6027</v>
       </c>
     </row>
     <row r="12">
@@ -752,16 +752,16 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>3.599503722084367</v>
+        <v>3.702007632321221</v>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F12" t="n">
         <v>4</v>
       </c>
       <c r="G12" t="n">
-        <v>6045</v>
+        <v>6027</v>
       </c>
     </row>
     <row r="13">
@@ -779,7 +779,7 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>2.753019023986766</v>
+        <v>2.746971959515514</v>
       </c>
       <c r="E13" t="n">
         <v>2</v>
@@ -788,7 +788,7 @@
         <v>3</v>
       </c>
       <c r="G13" t="n">
-        <v>6045</v>
+        <v>6027</v>
       </c>
     </row>
     <row r="14">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>3.037220843672456</v>
+        <v>3.538078646092583</v>
       </c>
       <c r="E14" t="n">
         <v>3</v>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G14" t="n">
-        <v>6045</v>
+        <v>6027</v>
       </c>
     </row>
     <row r="15">
@@ -833,7 +833,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>4.217866004962779</v>
+        <v>4.240584038493446</v>
       </c>
       <c r="E15" t="n">
         <v>5</v>
@@ -842,7 +842,7 @@
         <v>5</v>
       </c>
       <c r="G15" t="n">
-        <v>6045</v>
+        <v>6027</v>
       </c>
     </row>
     <row r="16">
@@ -860,7 +860,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>4.037220843672457</v>
+        <v>4.072507051601129</v>
       </c>
       <c r="E16" t="n">
         <v>5</v>
@@ -869,7 +869,7 @@
         <v>5</v>
       </c>
       <c r="G16" t="n">
-        <v>6045</v>
+        <v>6027</v>
       </c>
     </row>
     <row r="17">
@@ -887,7 +887,7 @@
         <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>2.422828784119107</v>
+        <v>2.429732868757259</v>
       </c>
       <c r="E17" t="n">
         <v>2</v>
@@ -896,7 +896,7 @@
         <v>3</v>
       </c>
       <c r="G17" t="n">
-        <v>6045</v>
+        <v>6027</v>
       </c>
     </row>
     <row r="18">
@@ -911,19 +911,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>3.925296833773087</v>
+        <v>4.491289198606272</v>
       </c>
       <c r="E18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G18" t="n">
-        <v>6064</v>
+        <v>6027</v>
       </c>
     </row>
     <row r="19">
@@ -938,19 +938,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>4.113621372031663</v>
+        <v>4.376306620209059</v>
       </c>
       <c r="E19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F19" t="n">
         <v>5</v>
       </c>
       <c r="G19" t="n">
-        <v>6064</v>
+        <v>6027</v>
       </c>
     </row>
     <row r="20">
@@ -965,19 +965,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>3.95976253298153</v>
+        <v>4.604612576738012</v>
       </c>
       <c r="E20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F20" t="n">
         <v>5</v>
       </c>
       <c r="G20" t="n">
-        <v>6064</v>
+        <v>6027</v>
       </c>
     </row>
     <row r="21">
@@ -995,16 +995,16 @@
         <v>3</v>
       </c>
       <c r="D21" t="n">
-        <v>3.147757255936675</v>
+        <v>3.177866268458603</v>
       </c>
       <c r="E21" t="n">
         <v>3</v>
       </c>
       <c r="F21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G21" t="n">
-        <v>6064</v>
+        <v>6027</v>
       </c>
     </row>
     <row r="22">
@@ -1019,19 +1019,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>3.067282321899736</v>
+        <v>3.774514683922349</v>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G22" t="n">
-        <v>6064</v>
+        <v>6027</v>
       </c>
     </row>
     <row r="23">
@@ -1046,19 +1046,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>3.888027704485488</v>
+        <v>4.1750456280073</v>
       </c>
       <c r="E23" t="n">
         <v>4</v>
       </c>
       <c r="F23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G23" t="n">
-        <v>6064</v>
+        <v>6027</v>
       </c>
     </row>
     <row r="24">
@@ -1073,19 +1073,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>2.70646437994723</v>
+        <v>3.693877551020408</v>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G24" t="n">
-        <v>6064</v>
+        <v>6027</v>
       </c>
     </row>
     <row r="25">
@@ -1103,7 +1103,7 @@
         <v>3</v>
       </c>
       <c r="D25" t="n">
-        <v>3.531827176781003</v>
+        <v>3.537746806039489</v>
       </c>
       <c r="E25" t="n">
         <v>3</v>
@@ -1112,7 +1112,7 @@
         <v>4</v>
       </c>
       <c r="G25" t="n">
-        <v>6064</v>
+        <v>6027</v>
       </c>
     </row>
     <row r="26">
@@ -1127,19 +1127,19 @@
         </is>
       </c>
       <c r="C26" t="n">
+        <v>4</v>
+      </c>
+      <c r="D26" t="n">
+        <v>3.566119130579061</v>
+      </c>
+      <c r="E26" t="n">
         <v>3</v>
       </c>
-      <c r="D26" t="n">
-        <v>2.924142480211082</v>
-      </c>
-      <c r="E26" t="n">
-        <v>2</v>
-      </c>
       <c r="F26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G26" t="n">
-        <v>6064</v>
+        <v>6027</v>
       </c>
     </row>
     <row r="27">
@@ -1154,19 +1154,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>3.298977572559367</v>
+        <v>3.67479674796748</v>
       </c>
       <c r="E27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F27" t="n">
         <v>4</v>
       </c>
       <c r="G27" t="n">
-        <v>6064</v>
+        <v>6027</v>
       </c>
     </row>
     <row r="28">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>2.546503957783641</v>
+        <v>3.532769205243073</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G28" t="n">
-        <v>6064</v>
+        <v>6027</v>
       </c>
     </row>
     <row r="29">
@@ -1211,7 +1211,7 @@
         <v>3</v>
       </c>
       <c r="D29" t="n">
-        <v>2.844986807387863</v>
+        <v>2.849676455948233</v>
       </c>
       <c r="E29" t="n">
         <v>2</v>
@@ -1220,7 +1220,7 @@
         <v>3</v>
       </c>
       <c r="G29" t="n">
-        <v>6064</v>
+        <v>6027</v>
       </c>
     </row>
   </sheetData>
@@ -1281,22 +1281,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.394775810721376</v>
+        <v>3.50482412477186</v>
       </c>
       <c r="C2" t="n">
-        <v>3.4</v>
+        <v>3.525</v>
       </c>
       <c r="D2" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="E2" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2908669755129054</v>
+        <v>0.2254853160776506</v>
       </c>
       <c r="G2" t="n">
-        <v>6044</v>
+        <v>6027</v>
       </c>
     </row>
     <row r="3">
@@ -1306,22 +1306,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.421027708850289</v>
+        <v>3.503225070516011</v>
       </c>
       <c r="C3" t="n">
-        <v>3.4</v>
+        <v>3.4625</v>
       </c>
       <c r="D3" t="n">
-        <v>2.125</v>
+        <v>2.3875</v>
       </c>
       <c r="E3" t="n">
         <v>4.6</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2489660876757651</v>
+        <v>0.1939605110336818</v>
       </c>
       <c r="G3" t="n">
-        <v>6045</v>
+        <v>6027</v>
       </c>
     </row>
     <row r="4">
@@ -1331,22 +1331,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.258610421836228</v>
+        <v>3.378853492616559</v>
       </c>
       <c r="C4" t="n">
-        <v>3.25</v>
+        <v>3.3875</v>
       </c>
       <c r="D4" t="n">
-        <v>2.05</v>
+        <v>2.4125</v>
       </c>
       <c r="E4" t="n">
-        <v>4.5625</v>
+        <v>4.449999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3655913978494624</v>
+        <v>0.2475526796084287</v>
       </c>
       <c r="G4" t="n">
-        <v>6045</v>
+        <v>6027</v>
       </c>
     </row>
     <row r="5">
@@ -1356,22 +1356,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.022140198511166</v>
+        <v>3.204583540733367</v>
       </c>
       <c r="C5" t="n">
-        <v>3.1375</v>
+        <v>3.3</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5625</v>
+        <v>1.675</v>
       </c>
       <c r="E5" t="n">
-        <v>4.337499999999999</v>
+        <v>4.487500000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4574028122415219</v>
+        <v>0.3641944582711133</v>
       </c>
       <c r="G5" t="n">
-        <v>6045</v>
+        <v>6027</v>
       </c>
     </row>
     <row r="6">
@@ -1381,22 +1381,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.481237631926121</v>
+        <v>3.876366766218682</v>
       </c>
       <c r="C6" t="n">
-        <v>3.4875</v>
+        <v>3.8</v>
       </c>
       <c r="D6" t="n">
-        <v>2.1625</v>
+        <v>2.7625</v>
       </c>
       <c r="E6" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2521437994722955</v>
+        <v>0.09407665505226481</v>
       </c>
       <c r="G6" t="n">
-        <v>6064</v>
+        <v>6027</v>
       </c>
     </row>
     <row r="7">
@@ -1406,22 +1406,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.971229798812665</v>
+        <v>3.514671478347436</v>
       </c>
       <c r="C7" t="n">
-        <v>2.875</v>
+        <v>3.5375</v>
       </c>
       <c r="D7" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="E7" t="n">
-        <v>4.3375</v>
+        <v>4.6</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5371042216358839</v>
+        <v>0.2769205243072839</v>
       </c>
       <c r="G7" t="n">
-        <v>6064</v>
+        <v>6027</v>
       </c>
     </row>
     <row r="8">
@@ -1431,22 +1431,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.588710009894459</v>
+        <v>3.098218433714949</v>
       </c>
       <c r="C8" t="n">
-        <v>2.5</v>
+        <v>3.0875</v>
       </c>
       <c r="D8" t="n">
-        <v>1.45</v>
+        <v>1.8625</v>
       </c>
       <c r="E8" t="n">
-        <v>3.975</v>
+        <v>4.3375</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7074538258575198</v>
+        <v>0.4519661523145844</v>
       </c>
       <c r="G8" t="n">
-        <v>6064</v>
+        <v>6027</v>
       </c>
     </row>
   </sheetData>
@@ -1515,10 +1515,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>569</v>
+        <v>3664</v>
       </c>
       <c r="D2" t="n">
-        <v>569</v>
+        <v>3664</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1531,11 +1531,11 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>wide_interval</t>
+          <t>supported</t>
         </is>
       </c>
     </row>
@@ -1549,23 +1549,23 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>732</v>
+        <v>15588</v>
       </c>
       <c r="D3" t="n">
-        <v>732</v>
+        <v>3004</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>variable_regime_public</t>
+          <t>variable_public_fallback</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>adequate</t>
+          <t>limited_regime_support</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -1583,10 +1583,10 @@
         <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>1106</v>
+        <v>3520</v>
       </c>
       <c r="D4" t="n">
-        <v>1106</v>
+        <v>3520</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1617,10 +1617,10 @@
         <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>524</v>
+        <v>5400</v>
       </c>
       <c r="D5" t="n">
-        <v>524</v>
+        <v>5400</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -1651,23 +1651,23 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>465</v>
+        <v>2748</v>
       </c>
       <c r="D6" t="n">
-        <v>23</v>
+        <v>2748</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>variable_public_fallback</t>
+          <t>variable_regime_public</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>limited_regime_support</t>
+          <t>adequate</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -1685,10 +1685,10 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>465</v>
+        <v>11691</v>
       </c>
       <c r="D7" t="n">
-        <v>97</v>
+        <v>2253</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1719,10 +1719,10 @@
         <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>247</v>
+        <v>2640</v>
       </c>
       <c r="D8" t="n">
-        <v>247</v>
+        <v>2640</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1753,23 +1753,23 @@
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>465</v>
+        <v>4050</v>
       </c>
       <c r="D9" t="n">
-        <v>98</v>
+        <v>4050</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>variable_public_fallback</t>
+          <t>variable_regime_public</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>limited_regime_support</t>
+          <t>adequate</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
